--- a/artfynd/A 51695-2023 artfynd.xlsx
+++ b/artfynd/A 51695-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51695-2023 artfynd.xlsx
+++ b/artfynd/A 51695-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122753468</v>
+      </c>
+      <c r="B3" t="n">
+        <v>86456</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Surråmyran SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>711871</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6654445</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Igenväxt kulturmark. Sälg, björk, hassel, gran. Örtrikt. Sårläka, blåsippa kransmossa.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 51695-2023 artfynd.xlsx
+++ b/artfynd/A 51695-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>122753468</v>
       </c>
       <c r="B3" t="n">
-        <v>86458</v>
+        <v>86462</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51695-2023 artfynd.xlsx
+++ b/artfynd/A 51695-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>122753468</v>
       </c>
       <c r="B3" t="n">
-        <v>86462</v>
+        <v>86465</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51695-2023 artfynd.xlsx
+++ b/artfynd/A 51695-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>122753468</v>
       </c>
       <c r="B3" t="n">
-        <v>86465</v>
+        <v>86467</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
